--- a/output/2026/scraped_data/Superintendency of Health 2026.xlsx
+++ b/output/2026/scraped_data/Superintendency of Health 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,37 +503,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Víctor Torres Jeldes</t>
+          <t>Tamara Andrea Núñez Andrewartha</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Superintendente de Salud</t>
+          <t>Jefa de la Unidad de Planificación, Innovación y Control de Gestión</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/466718/871292</t>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/259517/909060</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AO006AW2046724</t>
+          <t>AO006AW2180684</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-12 12:00:00-03</t>
+          <t>2026-05-12 12:00:00-04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>Videoconferencia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>QWxhbWVkYSAxNDQ5IHRvcmUgMiBwaXNvIDU=</t>
+          <t>Videoconferencia Teams</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,17 +543,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+          <t>Elaboración, tramitación, aprobación, modificación, derogación o rechazo de acuerdo, declaraciones o decisiones del Congreso Nacional o sus miembros incluídas comisiones.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Propuesta de conformación de una instancia colaborativa, en especial mesa con  los principales prestadores de salud (acreedores Ex Isapre Masvida),  y la Superintendencia de Salud, para el análisis situación jurídica de saldos no entregados a título excedentes conforme proceso contencioso administrativo rol 425-2018.</t>
+          <t>Nos encantaría presentarles la solución para el seguimiento analítico de expedientes y detección de fraudes en tiempo real que Newtenberg ha desarrollado para distintas instituciones del Estado.&lt;br /&gt;
+Nuestra solución se encuentra actualmente operando con éxito en el ISL y SUSESO y en fase piloto para la Superintendencia de Educación. Por lo mismo creemos sería de gran apoyo para el manejo análisis y administración de información en tiempo real que necesite utilizar su institución así como para la data histórica.&lt;br /&gt;
+En términos prácticos nuestra solución integra y extrae datos desde las fuentes primarias de información de la institución así como de fuentes externa que se requieran para construir un expediente.&lt;br /&gt;
+La principal ventaja de esta solución es que no requiere para su implementación de la modificación de los actuales sistemas que operan en la institución ni tampoco el desarrollo de nuevos sistemas para el manejo de los datos.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sergio Rojas Barahona</t>
+          <t>Marisol Docmac</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -561,14 +564,10 @@
           <t>Gestor de intereses</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Socofar S.A.</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Farmacias Cruz Verde SpA</t>
+          <t>NEWTENBERG PUBLICACIONES DIGITALES</t>
         </is>
       </c>
     </row>
@@ -585,7 +584,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Freddy Ramirez León</t>
+          <t>José Flores</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -593,31 +592,79 @@
           <t>Gestor de intereses</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Farmacias Cruz Verde S.A.</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Farmacias Cruz Verde SpA</t>
+          <t>NEWTENBERG PUBLICACIONES DIGITALES</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tamara Andrea Núñez Andrewartha</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jefa de la Unidad de Planificación, Innovación y Control de Gestión</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/259517/892335</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AO006AW2124287</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, Santiago, Chile - Metro La Moneda, Piso 5.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>En esta sesión exploraremos cómo la Inteligencia Artificial y el ecosistema de Google Workspace y Gemini Enterprise se convierten en los aliados estratégicos de la Unidad de Planificación Innovación y Control de Gestión. El objetivo es claro modernizar la operativa institucional para cumplir con excelencia el mandato regulador.&lt;br /&gt;
+&lt;br /&gt;
+1. Control de Gestión Inteligente y en Tiempo Real&lt;br /&gt;
+La dispersión de datos es un obstáculo para la fiscalización. Con Google Workspace centralizamos indicadores críticos en una fuente única de verdad. Visualice la consolidación de KPIs sobre tiempos de respuesta a reclamos y garantías de salud de forma automática. Esto permite a la jefatura tomar decisiones basadas en datos reales optimizando el cumplimiento de metas institucionales de manera proactiva.&lt;br /&gt;
+&lt;br /&gt;
+2. Gemini Enterprise IA para la Planificación y Normativa&lt;br /&gt;
+Analizar masivamente circulares resoluciones y planes operativos ya no requiere semanas de trabajo manual. Gemini Enterprise permite procesar grandes volúmenes de texto para identificar brechas de cumplimiento y generar borradores de planes anuales alineados con la Estrategia Nacional de Salud. Reducimos la carga administrativa permitiendo que el equipo se enfoque en el análisis estratégico y no en la transcripción.&lt;br /&gt;
+&lt;br /&gt;
+3. Hacia el Cero Papel y la Ley N 21.180&lt;br /&gt;
+Nuestra propuesta facilita el cumplimiento de la Ley de Transformación Digital. Habilitamos la interoperabilidad y la gestión de expedientes de fiscalización 100 digitales. No es solo tecnología es una evolución cultural hacia procesos ágiles que eliminan la burocracia física y mejoran la atención ciudadana.&lt;br /&gt;
+&lt;br /&gt;
+4. Seguridad de Clase Mundial Ley N 21.663&lt;br /&gt;
+La protección de datos sensibles de los beneficiarios es nuestra prioridad. Bajo la Ley Marco de Ciberseguridad la infraestructura de Google garantiza resiliencia y continuidad operativa ante cualquier incidente blindando la información contra amenazas externas.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>JUAN PABLO URIZUA RODRIGUEZ</t>
+          <t>Alejandro Nunez</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -627,335 +674,4381 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Farmacias Cruz Verde S.A.</t>
+          <t>Google for Education</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Farmacias Cruz Verde SpA</t>
+          <t>Google Chile Limitada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/914307</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AO006AW2184644</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:00:00-04</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Superintendencia de Salud - Alameda N° 1449 Torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos., 
+Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Solicitamos una audiencia para presentar una investigación sobre soledad perinatal desarrollada por investigadores de la Pontificia Universidad Católica de Chile en conjunto con el Centro de Políticas Públicas. El documento propone incorporar el Índice de Cuidado Mutuo como herramienta oficial de evaluación en los servicios de maternidad con el fin de medir y fortalecer la calidad relacional del cuidado perinatal.&lt;br /&gt;
+&lt;br /&gt;
+Creemos que esta audiencia es especialmente relevante dado que el Observatorio de Calidad en Salud aún no cuenta con métricas específicas para evaluar la dimensión relacional del cuidado aspecto que la investigación busca abordar.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Felipe Arriagada</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Pontificia Universidad Católica de Chile</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Pontificia Universidad Católica de Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>María Merino</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Pontificia Universidad Católica de Chile</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Pontificia Universidad Católica de Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/909162</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AO006AW2145879</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:00:00-04</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Superintendencia de Salud, Av. Bernardo O'Higgins (Alameda) Nº 1449, Edificio Santiago Downtown 2, Local 12, Santiago, piso 5.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Tramitación de procedimiento de reclamos por vulneración a la Ley 20.584 y 20.394 y posteriores procedimientos sancionadores así como los criterios y competencias de esta Intendencia.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Héctor Zavala</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Clínica Las Condes S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Paula Sepúlveda</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Clínica Las Condes S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901111</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AO006AW2128009</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:30:00-04</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Superintendencia de Salud - Intendencia de Prestadores, piso 5 -  Av. Libertador Bernardo O'Higgins Nº 1449, Edificio Santiago Downtown 2, Local 12, Santiago.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>EVALUACION DE LA INTENDENCIA RESPECTO DEL PROGRAMA DE CUMPLIMIENTO NORMATIVO IMPLEMENTADO PARA LOS SERVICIOS DE URGENCIA DE CLINICAS REDSALUD.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Marcelo Gallardo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>RED SALUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901116</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AO006AW2094490</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-02-27 12:30:00-03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALAMEDA 1449 TORRE 2 PISO 5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Le escribo para solicitar una reunión con el equipo técnico de la Intendencia de Prestadores respecto al numeral 207 del Compendio de Acreditación Hospitalaria Versión N6 Res. Exenta IPN7601 del 6 de diciembre de 2024 particularmente en lo que refiere al transporte de material estéril en vehículos.&lt;br /&gt;
+Creemos que una conversación directa nos permitiría abordar algunos puntos que son difíciles de transmitir adecuadamente por escrito. En concreto nos gustaría compartir&lt;br /&gt;
+Evidencia científica que respalda nuestra posición técnica sobre la preservación de la indemnidad del material.&lt;br /&gt;
+Un análisis de riesgos sobre cómo algunas soluciones exigidas actualmente podrían paradójicamente ir en contra del objetivo que todos compartimos que el material estéril llegue indemne al centro hospitalario.&lt;br /&gt;
+Propuestas concretas que aseguren el cumplimiento normativo y sobre todo resguarden la calidad de atención y seguridad del paciente.&lt;br /&gt;
+Valoramos mucho el trabajo de la Superintendencia y queremos contribuir constructivamente a la correcta implementación de estos estándares.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Nicolás Schnapp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Paraclinics s.a.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paraclinics SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901115</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AO006AW2094490</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-02-27 12:30:00-03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ALAMEDA 1449 TORRE 2 PISO 5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Le escribo para solicitar una reunión con el equipo técnico de la Intendencia de Prestadores respecto al numeral 207 del Compendio de Acreditación Hospitalaria Versión N6 Res. Exenta IPN7601 del 6 de diciembre de 2024 particularmente en lo que refiere al transporte de material estéril en vehículos.&lt;br /&gt;
+Creemos que una conversación directa nos permitiría abordar algunos puntos que son difíciles de transmitir adecuadamente por escrito. En concreto nos gustaría compartir&lt;br /&gt;
+Evidencia científica que respalda nuestra posición técnica sobre la preservación de la indemnidad del material.&lt;br /&gt;
+Un análisis de riesgos sobre cómo algunas soluciones exigidas actualmente podrían paradójicamente ir en contra del objetivo que todos compartimos que el material estéril llegue indemne al centro hospitalario.&lt;br /&gt;
+Propuestas concretas que aseguren el cumplimiento normativo y sobre todo resguarden la calidad de atención y seguridad del paciente.&lt;br /&gt;
+Valoramos mucho el trabajo de la Superintendencia y queremos contribuir constructivamente a la correcta implementación de estos estándares.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Nicolás Schnapp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Paraclinics s.a.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Paraclinics SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901114</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AO006AW2080397</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-02-26 15:30:00-03</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1. ACREDITACIÓN HOSPITAL SAN JOSE  INDEPENDENCIA&lt;br /&gt;
+2. RECURSO DE REPOSICIÓN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Alicia López</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Rodrigo Infante Cotroneo</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901119</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AO006AW2074783</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-02-26 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Solicitud de audiencia para plantear una inquietud de carácter técnico y administrativo en representación de una red de clínicas odontológicas relacionada con los procesos de Acreditación de Prestadores Institucionales bajo el Estándar de Atención Odontológica.&lt;br /&gt;
+&lt;br /&gt;
+Se busca exponer un análisis comparativo respecto de los costos asociados al arancel de acreditación para clínicas dentales los cuales actualmente son equivalentes a los de Centros de Atención Abierta de Baja Complejidad pese a que ambas categorías no resultan homologables desde una perspectiva técnica operativa de riesgo infraestructura y gestión.&lt;br /&gt;
+&lt;br /&gt;
+El objetivo de la reunión es presentar estos antecedentes y analizar la posibilidad de revisar a futuro una estructura de costos más acorde a la realidad de los prestadores exclusivos de atención odontológica promoviendo así una mayor adhesión al proceso de acreditación manteniendo altos estándares de calidad y seguridad asistencial.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Francisca Contreras</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sociedad Inmobiliaria y Comercial Uno Salud Limitada</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inversiones Dental Salud Spa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Paula Acuña</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inversiones Dental Salud Spa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Florencia López</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inversiones Dental Salud Spa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Camilo  Corral Guerrero</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Intendente de Prestadores de Salud</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/249764/901122</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AO006AW2067332</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-01-29 15:30:00-03</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALAMEDA 1449 TORRE 2 PISO 5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Art 12 y 13 de la Ley 20.584 acerca de la reserva de la información contenida en la ficha clínica. Secreto profesional. Código de ética de psicólogos de Chile.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Patricio Castillo Barrios</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Asociación Chilena De Seguridad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ana LEÓN</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Asociación Chilena De Seguridad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Luis Ignacio Vargas Franco</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Asociación Chilena De Seguridad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Asociación Chilena de Seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud (Primer orden de subrogancia)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/298398/901110</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AO006AW2144270</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:30:00-03</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/meet/21218997917841?p=xFKNVAWCsm7sJw7wQZ
+Id. de reunión: 212 189 979 178 41
+Código de acceso: rq7M2qR9</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>saludo protocolar y consultas de disponibilidad de información</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Matías Avendaño</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Asociación de Isapres de Chile A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Patricio Valdivia</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Asociación de Isapres de Chile A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Osvaldo Varas</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/910542</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AO006AW2184307</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5°, Santiago Centro (Metro La Moneda - Salida Amunategui)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Revisión de normativa aplicable a generación de 5 por ciento de excedentes  Ley 21.674&lt;br /&gt;
+Resoluciones Superintendencia de Salud que regulan el tema de generación de excedentes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>FELIPE Martínez</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Isapre Banmédica S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Gonzalo Pulido</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Isapre Banmédica S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/910540</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AO006AW2183892</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:00:00-04</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5° (Metro La Moneda-Salida Amunategui)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Consulta formulada sobre revisión de planes grupales</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Gonzalo Claudio Arriagada Lillo</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Rosa Rojas Cabello</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Empresas Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Aldo Andrés Corradossi Balboni</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Optima S.A.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Fuad Chahin</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ENZO QUEIROLO</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Empresas Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/908331</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AO006AW2181393</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Piso 5, Santiago Centro (Metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Nueva Normativa PAD</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>CONSUELO SALINAS JARA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>María del Pilar Crosgrove</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Claudia Campos</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/907863</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AO006AW2181422</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-11 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Piso 5, Santiago Centro (Metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Caso Hospitalización Domiciliaria</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Francisco González</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Isapre Consalud S.A.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Elizabeth Miranda</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Fernando Silva</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/903325</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AO006AW2175297</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:00:00-04</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Santiago</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0 horas, 30 minutos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Presentación de propuesta Isapre Colmena sobre IBNR y normas Circular IF 140.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Luz Román</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross S. A.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ramiro Sánchez Tuculet</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/901106</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AO006AW2144442</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alameda 1449 Torre II Piso 5 (Salida Metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Proceso de pronto pago a realizarse para deuda TFU que Nueva Masvida ejecutará de acuerdo a lo dispuesto en el Plan de Pago y Ajustes aprobado por la Superintendencia de Salud</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Fuad Chahin</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Fuad Chahin Valenzuela</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CARLOS JARA ULLOA</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Aldo Andrés Corradossi Balboni</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ronny Hernández</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/897757</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AO006AW2136678</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-04-14 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5° (salida metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Buenas tardes quisiéramos solicitar una reunión para poder acordar algún procedimiento de entrega por parte de las isapres del Sensor de glucosa  código Fonasa 2301074 el cual fue incluido en la canasta Ges de Diabetes Tipo 1 el 1 de diciembre del año 2025. A la fecha no existe conocimiento en todas las isapres de esta entrega por Ges dando respuesta a los pacientes de que no esta en la canasta o que aún no se puede entregar que no tiene cobertura GES o que aun no esta en el sistema.&lt;br /&gt;
+El objetivo seria lograr que cada Isapre informe vía email la forma de retirar este insumo y los pasos que se deberían seguir por ejemplo llevar receta primero a la isapre timbrarla etc. En definitiva formalizar el procedimiento de entrega de este dispositivo.&lt;br /&gt;
+&lt;br /&gt;
+Más abajo les dejamos un listado de los pacientes que tenemos registro nos han reclamado. Esperamos una buena acogida y muchas gracias de antemano.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maria Pia Zaldivar Prado</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>FUNDACION DIABETES FUTURO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/897759</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AO006AW2140098</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:00:00-04</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5° (salida metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Plantear una serie de dudas respecto a la forma en como dar cumplimiento a una serie de sentencias dictadas por el Señor Intendente como Juez Arbitro en el marco de la Ley Ricarte Soto.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ALFREDO LEONARDO OSSA DE LA LASTRA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>FUNDACION DEBRA CHILE NIÑOS PIEL DE CRISTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Rosario Dell Oro</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Fundación DEBRA Chile</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>FUNDACION DEBRA CHILE NIÑOS PIEL DE CRISTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bernardita Aspillaga</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Fundación DEBRA Chile</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Fundación Debra Chile Niños Piel de Cristal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/890983</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AO006AW2118244</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-03-19 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ingreso por Alameda 1449, Torre 2, Piso 5, Santiago (Metro La Moneda).</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ordinario N 8121</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Francisco González</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Isapre Consalud S.A.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Víctor Moreno Morales</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/890984</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AO006AW2105787</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-03-18 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, Piso 5 (Metro la Moneda)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Materias financieras Isapre Colmena tales como full IFRS garantías entre otras.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Luz Román</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross S. A.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ramiro Sánchez Tuculet</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross S. A.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Carlos Fabres Osses</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross S. A.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS AS.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Carola Schwencke Reyes</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/890985</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AO006AW2104315</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-03-17 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Normativa Isapres</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Gabriela Yolanda Novoa Muñoz</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS Servicios Clínicos SpA</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS SERVICIOS CLINICOS SPA  RED DE SALUD UC CHRISTUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Alejandro Corvalán</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS SERVICIOS CLINICOS SPA RED DE SALUD UC CHRISTUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Thomas Leisewitz Velasco</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS SERVICIOS CLINICOS SPA RED DE SALUD UC CHRISTUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Felipe Galleguillos Serey</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS Servicios Clínicos SpA</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>UC CHRISTUS SERVICIOS CLINICOS SPA RED DE SALUD UC CHRISTUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/885307</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AO006AW2096854</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-02-26 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Rechazo a Alza de cotización GES afiliados a Isapre Isalud Isapre de Codelco.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Hernán Marcos Guerrero Maluenda</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>CODELCO CHILE DIVISION EL TENIENTE</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Sindicato De trabajadores Chuquicamata División Chuquicamata</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Jeannette Astudillo</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Sindicato de Trabajadores Chuquicamata División Chuquicamata</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/881692</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AO006AW2090747</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-02-19 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alameda N° 1449, -Torre II, piso 5 ( Metro La Moneda, Salida Amunategui)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Parámetros y aplicación de tope de 5 por ciento de cotización legal para generación de excedentes</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Aldo Andrés Corradossi Balboni</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Marcelo Castro</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/881691</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AO006AW2066375</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-02-19 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Proceso de desafiliación de acuerdo a lo dispuesto en la letra f  del Título VI Reglas en materia de terminación de contratos del Capítulo I Procedimientos Relativos al Contrato de Salud del Compendio de Procedimientos.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Fuad Chahin</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Fuad Chahin Valenzuela</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Aldo Andrés Corradossi Balboni</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Felipe Correa</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Osvaldo Varas</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/874465</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>AO006AW2059690</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>2026-01-22 10:00:00-03</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>QWxhbWVkYSAxNDQ5IHRvcnJlIDIgcGlzbyA1IA==</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alameda 1449 torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Consultar respecto de cuestiones relativas al reparto de los montos de la garantía de la quiebra de la ex isapre Masvida.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Felipe Ayala Manriquez</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Claudio de Amesti</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Osvaldo Varas</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/872662</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>AO006AW2055752</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>2026-01-15 10:00:00-03</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>QWxhbWVkYSAxNDQ5LCBUb3JyZSBJSSwgUGlzbyA1wrAgKFNhbGlkYSBNZXRybyBMYSBNb25lZGEp</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre II, Piso 5° (Salida Metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Presentar al Sr. Intendente de Fondos cuatro  propuestas técnicas para mejorar la gestión de las garantías financieras de la Isapre.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Ramiro Sánchez Tuculet</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>Colmena Golden Cross S. A.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Colmena Golden Cross S. A</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Carlos Fabres Osses</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>Colmena Golden Cross S. A.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Colmena Golden Cross S. A.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Osvaldo Varas</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Intendente de Fondos y Seguros Previsionales de Salud</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/11141/870579</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>AO006AW2048796</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>2026-01-06 10:00:00-03</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>QWxhbWVkYSBOwrAgMTQ0OSwgVG9ycmUgSUksIFBpc28gNSAoU2FsaWRhIE1ldHJvIExhIE1vbmVkYSk=</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alameda N° 1449, Torre II, Piso 5 (Salida Metro La Moneda)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Abordar los criterios para la definición de los casos en que se considera que se han impetrado beneficios que no corresponden y que habiliten a las instituciones de salud previsional a poner término al contrato de salud, en los términos establecidos en el DFL N° 1 de salud. lo anterior, en el contexto de los casos correspondientes a fiscalización SUSESO.&lt;br /&gt;
 Elementos necesarios para acreditación de dicha circunstancia.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Fuad Chahin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>Fuad Chahin Valenzuela</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Nueva Masvida</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Marcelo Castro</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
         <is>
           <t>Nueva Masvida</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Ricardo Cuevas</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Encargado Subdepartamento de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/914212</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AO006AW2184541</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl, pcatalan@superdesalud.gob.cl, tsalgado@superdesalud.gob.cl, tnunez@superdesalud.gob.cl, rduarte@superdesalud.gob.cl, ehidalgo@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ADManager Plus de ManageEngine ayuda a estar preparado para cumplir con las leyes de protección de datos como RGPD LOPD HIPAA SOX al permitir la administración segura de identidades la auditoría completa de AD Active Directory y la rápida recuperación de objetos esencial para incidentes de seguridad y solicitudes de derecho al olvido.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Maria Alicia Araya Jorquera</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Nombre o razón social   SOCIEDAD DE SERVICIOS COMPUTACIONALES MICROSERV LIMITADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Christian Leyton</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE SERVICIOS COMPUTACIONALES MICROSERV LIMITADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Freddy Rojas</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE SERVICIOS COMPUTACIONALES MICROSERV LIMITADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/910697</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AO006AW2173492</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-05-13 11:00:00-04</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Esta reunión se realizará en dependencias de la Superintendencia de Salud en Av. Libertador Bernardo O’Higgins 1449, Torre 2, Piso 5, (Metro La Moneda).</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Hola Ricardo espero que estés muy bien.&lt;br /&gt;
+&lt;br /&gt;
+Te escribo para retomar la charla que tuvimos en Interoperabilidad 2024. Aprovechando que estaré de visita la semana del 11 de mayo me encantaría que pudiéramos reunirnos brevemente.&lt;br /&gt;
+&lt;br /&gt;
+Estamos desembarcando con fuerza en Chile tras haber sido elegidos por una gran red de clínicas para implementar nuestro HIS en toda su operación. Este proyecto ha sido clave para adaptar nuestra tecnología al 100 a la realidad local.&lt;br /&gt;
+&lt;br /&gt;
+Me gustaría mucho conocer sus proyectos para 2025 y compartirte cómo en K2BHealth estamos impulsando la transformación digital. A través de Dandelion nuestra plataforma de interoperabilidad basada en FHIR logramos una visión 360 del paciente en tiempo real integrando además IA para optimizar la toma de decisiones y la eficiencia operativa.&lt;br /&gt;
+&lt;br /&gt;
+Tendrás un hueco en tu agenda esa semana para un café o una reunión corta&lt;br /&gt;
+&lt;br /&gt;
+Un saludo&lt;br /&gt;
+&lt;br /&gt;
+Priscilla</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Priscilla Lima</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Genexus Consulting SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/910654</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AO006AW2183498</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:00:00-04</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Esta reunión se realizará en dependencias de la Superintendencia de Salud en Av. Libertador Bernardo O’Higgins 1449, Torre 2, Piso 5, (Metro La Moneda).</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Revisar posible adquisición de licenciamiento de Copilot 365 basándonos en las nuevas funcionalides que están disponibles dentro de la herramienta de Inteligencia Artificial de Microsoft. Por otro lado explorar iniciativa de implementación de un caso particular que podría ser abordado con Copilot.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Esteban Mercado</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Consultoría ReadyMind Limitada</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ESTEBAN MERCADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ALVARO JAVIER BRIONES NAVARRETE</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>CONSULTORIA READYMIND LIMITADA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/910658</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AO006AW2180584</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:00:00-04</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl, mcarrasco@superdesalud.gob.cl, pcatalan@superdesalud.gob.cl, tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Buen día Ricardo. Somos ATCOM con 34 años de trayectoria y presencia en Convenio Marco. Solicitamos audiencia para presentar nuestra propuesta en Outsourcing de perfiles TI y servicios especializados de Ciberseguridad. Nuestro objetivo es apoyar sus objetivos estratégicos y el cumplimiento normativo mediante la mitigación de riesgos y la provisión de talento crítico. Quedamos atentos a su disposición.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Angelina Morales</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Atcom Outsourcing SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/906109</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AO006AW2128878</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-05-05 10:30:00-04</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Presentar apoyo en el ambito de networking ciberseguridad cloud y cumplimiento normativo. Entender las dificultades y problemas recurrentes de la superintendencia para diseñar plan de apoyo y generar apoyo tecnologico</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Cristian Fuentes</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Group 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Matias Ignacio Muñoz Soto</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Group 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/903708</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AO006AW2123958</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:30:00-04</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@supedesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Presentación de nuestra solución tecnológicas  para Trazabilidad Médica diseñada para gestionar la trazabilidad de dispositivos médicos cumpliendo con las normativas vigentes del Ministerio de Salud particularmente la Norma General Técnica N226 trazabilidad de dispositivos médicos en prestadores de salud y la Norma General Técnica N247 sobre trazabilidad y seguridad del paciente junto con Trazalogis WMS nuestra plataforma de gestión de bodegas y logística.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Maria José Molina Sanchis</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Iotec LTDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/900971</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AO006AW2117789</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-04-21 12:00:00-04</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , rsierra@superdesalud.gob.cl , pcastillo@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PuntoSeguro es una empresa chilena con más de 20 años de experiencia en soluciones de gestión de asistencia para instituciones públicas y privadas.&lt;br /&gt;
+Solicitamos la reunión para presentar nuestro módulo de gestión y administración de asistencia orientado al cumplimiento normativo trazabilidad y eficiencia en la gestión de la jornada laboral del personal y explorar posibles oportunidades de colaboración.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Jorge Valenzuela</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Soluciones en Seguridad Limitada</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Soluciones en Seguridad Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Andrea Tejos</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Soluciones en Seguridad Limitada</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Soluciones en Seguridad Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/899025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AO006AW2147040</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:30:00-04</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>En Av. Libertador Bernardo O´higgins 1449 Torre 2 piso 5 Santiago Centro.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Desde AWS y su vertical de salud nos gustaría poder conversar acerca de los nuevos desafíos 2026 de la superintendencia junto con validar como la tecnología y en particular la Inteligencia Artificial puede apoyar en la consecución de resultados. Eventualmente efectuar alguna prueba de concepto para validar casos de usos y KPI de interés.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Fabián Luengo</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Servicios Amazon Web Services Chile Ltda.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Servicios Amazon Web Services Chile Limitada</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Jose Gardiazabal</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Servicios Amazon Web Services Chile Ltda.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Servicios Amazon Web Services Chile Limitada</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/895452</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AO006AW2114066</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-04-07 10:30:00-04</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , aramirez@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Se solicita reunion para presentar nuestros servicios TI principalmente en Infraestructura Call y Contac Center basados en IA</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Claudio Escobar</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Espex ingeniería Limitada</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Espex Ingeniería Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/895451</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AO006AW2138352</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:00:00-04</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>En Av. Libertador Bernardo O´Higgins 1449 Torre 2 piso 5 Santiago Centro.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Presentación del Centro Nacional en Sistemas de Información en Salud con enfásis en temas de innovación.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Alejandra Luisa García Acevedo</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Centro Nacional en Sistemas de Información en Salud  CENS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/894646</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AO006AW2090971</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Favor enviar link para reunión virtual rcuevas@superdesalud.gob.cl
+tsalgado@superdesalud.gob.cl ,  pcatalan@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Estimados&lt;br /&gt;
+En Optimiza Seguridad representantes oficiales de Zimbra en Chile nos dirigimos a ustedes para presentar una alternativa robusta y costoefectiva frente a soluciones tradicionales como Microsoft Office 365 o Google Workspace.&lt;br /&gt;
+Nuestra solución de Correo Colaborativo Zimbramail destaca por&lt;br /&gt;
+Eficiencia Económica Planes competitivos desde 21 USD anuales por usuario.&lt;br /&gt;
+Soberanía y Seguridad Operación 100 en Data Centers nacionales.&lt;br /&gt;
+Soporte Premium Asistencia técnica local 247 garantizando continuidad operativa.&lt;br /&gt;
+Integralidad Incluye Mail Drive Videoconferencia Ofimática Calendario y Gestión de Archivos.&lt;br /&gt;
+Nos interesa agendar una breve audiencia para conocer sus necesidades específicas y mostrarles cómo nuestra solución puede optimizar su presupuesto. Cabe destacar que ya nos encontramos disponibles en el Convenio Marco de Licencias de Software de Ofimática facilitando cualquier proceso de adquisición.&lt;br /&gt;
+Mas información en&lt;br /&gt;
+Nuestra Página httpswww.zimbramail.cl&lt;br /&gt;
+LinkedIn httpswww.linkedin.comcompanyzimbraemail&lt;br /&gt;
+Convenio Marco httpsofimaticav4.mercadopublico.clofimatica4licencia4193070</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Cristian Campos</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Optimiza Seguridad</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Optimiza Seguridad SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/899020</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AO006AW2107014</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , mcarrasco@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Estimado Ricardo&lt;br /&gt;
+&lt;br /&gt;
+Espero estés muy bien. Solicito una audiencia para presentar a ZerviZ y nuestras capacidades en el ámbito de Tecnologías de la Información orientadas a apoyar a instituciones públicas en sus desafíos de modernización digital continuidad operacional y fortalecimiento de sus plataformas tecnológicas.&lt;br /&gt;
+ZerviZ es una empresa tecnológica con experiencia en Cloud Computing arquitectura TI y transformación digital que acompaña a organismos del Estado en el diseño e implementación de soluciones tecnológicas alineadas a los marcos normativos del sector público. Actualmente trabajamos con distintas instituciones públicas como Gobiernos Regionales Metropolitano GORE MINAGRI ChileAtiende SAG entre otras apoyando iniciativas vinculadas a infraestructura en la nube continuidad operacional y servicios digitales. Asimismo somos partner de AWS lo que nos permite respaldar técnicamente este tipo de iniciativas.&lt;br /&gt;
+El objetivo de la audiencia es darnos a conocer compartir nuestra experiencia y comprender las prioridades tecnológicas de la institución para poder orientar así como hemos orientado a grandes entidades gubernamentales.&lt;br /&gt;
+&lt;br /&gt;
+Quedo atento a su disponibilidad para que conversemos.&lt;br /&gt;
+Saludos&lt;br /&gt;
+&lt;br /&gt;
+ZerviZ.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Cristobal Llabres Ilufi</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ZerviZ Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/891470</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AO006AW2106772</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Enviar link para la reunión a: rcuevas@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl , mcarrasco@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0 horas, 30 minutos</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Hacknoid es una plataforma de gestión de vulnerabilidades con remediación e IA. &lt;br /&gt;
+Solicitamos una reunión para conversar sobre medidas concretas que permitan fortalecer la ciberseguridad del organismo con foco en &lt;br /&gt;
+Gestión de vulnerabilidades &lt;br /&gt;
+Priorización efectiva de riesgos y &lt;br /&gt;
+Automatización en la remediación. &lt;br /&gt;
+En un escenario donde la IA está transformando tanto la operación como las amenazas Hacknoid incorpora esta capacidad como una capa superior para entregar información más inmediata y mejorar la eficiencia con que los equipos identifican entienden y atienden sus exposiciones más críticas</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Rosina Ordoqui</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Hacknoid SPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Agustin Pedrosa</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Hacknoid</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/889352</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AO006AW2101021</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-03-18 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Enviar links a: rcuevas@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Mostrar y ofrecer nuestro programa y servicios de ciberseguridad para cumplir con la ley 21.663.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Sebastian Carbonell</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Sebastian Carbonell</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Raúl Alexis Muñoz Tolosa</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Raul Muñoz</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/882853</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AO006AW2067750</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos., 
+Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento., 
+Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Realizaremos presentación sobre Ley Marco de Ciberseguridad e Infraestructura crítica de la Información y Soluciones para dar cumplimiento a la normativa vigente en Ciberseguridad a través de implementación de herramientas tecnológicas e implementación de estándares. La norma ya fue promulgada y publicada el 08 de Abril de 2024. Entró en total y absoluta vigencia el 01 de Marzo del 2025 incluyendo el régimen sancionatorio Reglamento Decretos e Instrucción n1. Es completamente aplicable a toda la Administración del Estado Públicas de Chile estableciendo obligaciones y cumplimiento de estándares tanto a Servicios Esenciales como a Operadores de Importancia Vital con graves sanciones para quienes no den cumplimiento a ésta normativa. &lt;br /&gt;
+Los solicitantes somos de Concepción agradeceremos nos otorguen reunión vía telemática.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Daniel Del Desposito</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Daniel del Despósito Clunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Patricio Del Desposito</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Patricio del Despósito Clunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Benjamín Cataldo</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SISINF Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ricardo Cuevas</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Encargado Subdepartamento de Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/875533</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>AO006AW2052060</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>2026-01-27 11:30:00-03</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Videoconferencia</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>RW52aWFyIGxpbmsgYTogcmN1ZXZhc0BzdXBlcmRlc2FsdWQuZ29iLmNsICwgIHBjYXRhbGFuQHN1cGVyZGVzYWx1ZC5nb2IuY2wgLCB0c2FsZ2Fkb0BzdXBlcmRlc2FsdWQuZ29iLmNs</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl ,  pcatalan@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>0 horas, 30 minutos</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Primero que todo, me presento: soy Margarita Ávalos, ejecutiva comercial en Adis Chile, empresa con 20 años de experiencia en el rubro tecnológico.&lt;br /&gt;
 &lt;br /&gt;
@@ -968,174 +5061,174 @@
 Por lo anterior me encantaría coordinar una reunión con tu equipo para presentarles en detalle nuestro alcance y las novedades que manejamos actualmente.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Margarita Ávalos</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
         <is>
           <t>Adis Chile Ltda</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Ricardo Cuevas</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Encargado Subdepartamento de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/874707</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>AO006AW2056096</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>2026-01-22 11:00:00-03</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Videoconferencia</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>RW52aWFyIGxpbmsgYTogcmN1ZXZhc0BzdXBlcmRlc2FsdWQuZ29iLmNsICwgdHNhbGdhZG9Ac3VwZXJkZXNhbHVkLmdvYi5jbCAsIHBjYXRhbGFuQHN1cGVyZGVzYWx1ZC5nb2IuY2w=</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl , pcatalan@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Presentación de Adaptive Security, empresa chilena de ciberseguridad</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Rodrigo Bouffanais</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>Verisure Chile SpA</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>ADAPTIVE SECURITY</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
         <is>
           <t>Miguel Rosales</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>Adaptive Security SpA</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>ADAPTIVE SECURITY</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Ricardo Cuevas</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Encargado Subdepartamento de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/873793</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>AO006AW2055354</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>2026-01-20 10:00:00-03</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Videoconferencia</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>RW52aWFyIGxpbmsgYTogcmN1ZXZhc0BzdXBlcmRlc2FsdWQuZ29iLmNsICwgdHNhbGdhZG9Ac3VwZXJkZXNhbHVkLmdvYi5jbCAsIG1jYXJyYXNjb0BzdXBlcmRlc2FsdWQuZ29iLmNs</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl , mcarrasco@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>FEBOS &lt;br /&gt;
 Plataforma Integral de Gestión Documental, Ciudadana y Compras. &lt;br /&gt;
@@ -1153,74 +5246,74 @@
 Nuestro equipo Técnico y Comercial los acompañará durante toda la prestación del servicio (levantamiento, parametrización, pruebas, puesta en marcha, capacitación y soporte), garantizando un uso eficiente, cumplimiento normativo y mejorando la vida de los funcionarios y ciudadanos.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Cristian Mera</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>FEBOS AMI SPA</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>FEBOS AMI SPA</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Ricardo Cuevas</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Encargado Subdepartamento de Tecnologías de la Información</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/325594/873972</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>AO006AW2059122</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>2026-01-13 16:00:00-03</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Videoconferencia</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>RW52aWFyIGxpbmsgYTogcmN1ZXZhc0BzdXBlcmRlc2FsdWQuZ29iLmNsICwgdHNhbGdhZG9Ac3VwZXJkZXNhbHVkLmdvYi5jbA==</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl , tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Estimados&lt;br /&gt;
 &lt;br /&gt;
@@ -1237,122 +5330,3336 @@
 Carolina</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Carolina Uribe</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>SONDA S.A.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>Sonda</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Jorge Dip</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Fiscal</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/498884/901102</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AO006AW2101318</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:00:00-03</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Continuación propuesta colaborativa de análisis jurídico de saldos no entregados a título de excedentes conforme proceso contencioso administrativo rol 425 2018</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Sergio Rojas Barahona</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Socofar S.A.</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Francisca Cea Besoaín</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Jorge Dip</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/498884/870441</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>AO006AW2052038</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>2026-01-08 10:00:00-03</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>QWxhbWVkYSAxNDQ5LCB0b3JyZSAyIHBpc28gNSA=</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>1 horas, 0 minutos</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Jerárquico de la resolución 12000</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Roberto Sotomayor</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t>ISALUD ISAPRE DE CODELCO</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>ISALUD ISAPRE DE CODELCO SpA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
         <is>
           <t>Gustavo Morales Hidalgo</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Gestor de intereses</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Rodrigo Sierra</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Jefe de Departamento de Administración y Finanzas</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/333622/914210</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AO006AW2174486</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:30:00-04</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Enviar link a: rcuevas@superdesalud.gob.cl ; fpalacios@superdesalud.gob.cl ; cgutierrez@superdesalud.gob.cl ; tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Estimado Rodrigo&lt;br /&gt;
+Me dirijo a usted en representación de Locsite especializados en consultoría y gestión inmobiliaria con más de 15 años de experiencia y casos exitosos en el ámbito público y privado&lt;br /&gt;
+Nuestra labor como intermediador inmobiliario ha permitido a diversas instituciones identificar oportunidades que optimizan tanto el uso de espacios como la eficiencia de costos siempre bajo criterios de transparencia y alineados con las normativas vigentes apoyando a las unidades en la lógica del ajuste presupuestario conocido y las diferentes alternativas que mercado presenta.&lt;br /&gt;
+Nos gustaría poder sostener una conversación sobre alternativas de oficinas vigentes que pueden generar beneficios significativos para ustedes al facilitar&lt;br /&gt;
+&lt;br /&gt;
+Reducción de costos operativos mediante oficinas más eficientes o unificaciones en un solo edificio&lt;br /&gt;
+Mejor aprovechamiento de infraestructura existente con soluciones adaptadas a las necesidades institucionales bajo renegociaciones de contrato.&lt;br /&gt;
+Procesos de gestión claros y estratégicos respaldados por experiencia comprobada en procesos con entidades gubernamentales en los últimos 4 años donde destacan la Tesorería General de la República Dirección de Concesiones del MOP Superintendencia de Educación Superior entre otros&lt;br /&gt;
+&lt;br /&gt;
+Nos encantaría coordinar una reunión en el marco de la Ley del Lobby para presentar en detalle cómo Locsite puede aportar en conseguir el ajuste y reducción de costos.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Javier Rojas Rojas</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Intermediación y Consultoría Inmobiliaria Locsite Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Enrique Del Campo</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Intermediación y Consultoría Inmobiliaria Locsite Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Rodrigo Sierra</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jefe de Departamento de Administración y Finanzas</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/333622/891462</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AO006AW2124526</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-03-25 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Enviar link a: rsierra@superdesalud.gob.cl , karriagada@superdesalud.gob.cl , flefever@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Elaboración, tramitación, aprobación, modificación, derogación o rechazo de acuerdo, declaraciones o decisiones del Congreso Nacional o sus miembros incluídas comisiones.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Estimado junto con saludar en su momento tuve reunión con ustedes en la cual quedamos de realizar el convenio pero lamentablemente nunca tuve retorno con la documentación para realizarlo agradecería poder retomar las gestiones con ustedes y tener una nueva audiencia.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Yasna Contreras</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>yasna contreras silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Rodrigo Sierra</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jefe de Departamento de Administración y Finanzas</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/333622/888666</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AO006AW2095398</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:00:00-03</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Enviar link a: rsierra@superdesalud.gob.cl ; jserey@superdesalud.gob.cl ; tsalgado@superdesalud.gob.cl</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Estimada. Esta solicitud de lobby va dirigida a Rodrigo Sierra.&lt;br /&gt;
+&lt;br /&gt;
+Junto con saludar me pareció interesante solicitar esta audiencia de lobby para poder presentarles Buk nuestro software de Gestión de Personas. Nosotros en este software tenemos módulos de remuneraciones control de asistencia firma digital onboarding canal de denuncias selección comunicación gestión del desempeño encuestas capacitaciones entre otros. Estamos al día con la normativa vigente y ya trabajamos con más de 120 instituciones públicas. &lt;br /&gt;
+&lt;br /&gt;
+Este espacio es para presentarles cómo funciona Buk y en la misma línea entender qué necesitan para su gestión de personas. &lt;br /&gt;
+&lt;br /&gt;
+Si les parece podemos coordinar esta reunión de 60 minutos que será en modalidad online.  Cuéntenme qué día y a qué hora les acomoda para enviar el link de la reunión. Nosotros tenemos disponibilidad este viernes a las 10 12 y 14 hrs. &lt;br /&gt;
+Quedo muy pendiente de su respuesta.&lt;br /&gt;
+Saludos y muchas gracias&lt;br /&gt;
+&lt;br /&gt;
+valonsobuk.cl</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Valentina Alonso</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Buk SpA</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Buk Spa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Víctor Torres Jeldes</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/466718/882597</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AO006AW2078099</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-02-02 16:00:00-03</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>La Resolución Exenta 1541 de fecha 22 de diciembre de 2025. Verificaciones.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Gonzalo Claudio Arriagada Lillo</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Víctor Torres Jeldes</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/466718/871292</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AO006AW2046724</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:00:00-03</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alameda 1449 tore 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Propuesta de conformación de una instancia colaborativa, en especial mesa con  los principales prestadores de salud (acreedores Ex Isapre Masvida),  y la Superintendencia de Salud, para el análisis situación jurídica de saldos no entregados a título excedentes conforme proceso contencioso administrativo rol 425-2018.</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Sergio Rojas Barahona</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Socofar S.A.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Freddy Ramirez León</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde S.A.</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>JUAN PABLO URIZUA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Lobista</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>FEMSA SALUD SPA</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Farmacias Cruz Verde SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/920242</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AO006AW2197224</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:30:00-04</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alame 1449</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Reunión protocolar</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Macarena Bravo</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Optima S.A.</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Aldo Andrés Corradossi Balboni</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Optima S.A.</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Fuad Chahin</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>CARLOS JARA ULLOA</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/914304</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AO006AW2190553</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:30:00-04</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Presentación de la Federación Médica de Chile mirada del mundo medico de la salud privada dialogo gestión y disposición de trabajo</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Gonzalo Simón Bustos</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>asociacion de isapres de chile</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Federación Medica de Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Rodrigo Julio</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Federacion Medica de Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Ignacio Castillo</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Federacion Medica de Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/914302</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AO006AW2180725</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:30:00-04</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Consideraciones sobre el sistema de salud y labor de los prestadores privados. Espacios para favorecer la complementariedad público privada en el sistema de salud.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>José Ignacio Valenzuela Bozinovich</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>CLINICA DAVILA Y SERVICIOS MEDICOS S.A.</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>CLÍNICAS DE CHILE A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Javier Fuenzalida Santander</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>CLÍNICAS DE CHILE A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Cristian De La Fuente</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>CLÍNICAS DE CHILE A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/909163</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AO006AW2173300</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:30:00-04</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Presentación Isapre Colmena ante el Sr. Superintendente.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Luz Román</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross S. A.</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Ramiro Sánchez Tuculet</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Carola Schwencke Reyes</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/909164</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AO006AW2172217</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:30:00-04</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Presentar a Bupa e intercambiar visiones sobre los desafíos y oportunidades del sistema de salud.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Javier Schulz</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Bupa Chile S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/902302</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AO006AW2152963</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-04-22 15:30:00-04</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alameda 1149 torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Saludo protocolar de Isapre Isalud</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Roberto Sotomayor</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Gustavo Morales Hidalgo</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Alejandro Becker Gálmez</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/901103</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AO006AW2149086</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:30:00-04</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Presentación ante el Superintendente de Salud&lt;br /&gt;
+Información sobre propuesta de algunas iniciativas para el mercado asegurador de Isapres</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Nicolas Cabello Eterovic</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Banmedica S.A.</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Isapre Banmédica S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Aldo Gaggero</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Isapre Banmédica S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/901105</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AO006AW2147222</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:00:00-04</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2, piso 5</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento., 
+Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Presentación institucional de Esencial ante el nuevo Superintendente y el nuevo Gerente General de la Isapre.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Andrés Guimpert Guridi</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Marcela Palma</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Fernando Riveros</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Superintendente de Salud</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/902474/901100</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AO006AW2147611</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:30:00-04</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alameda 1449, Torre 2 piso 5</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>saludos protocolares</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Gonzalo Claudio Arriagada Lillo</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Asociación de Isapres de Chile A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Matías Avendaño</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Asociación de Isapres de Chile A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Gabriela Sandoval</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Asociación de Isapres de Chile A.G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/904386</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AO006AW2160116</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-04-30 10:00:00-04</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>0 horas, 45 minutos</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos., 
+Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>abordar y revisar distintos aspectos relacionados con proceso de metas del Examen de Medicina Preventiva EMP para el año 2026.&lt;br /&gt;
+En particular nos gustaría poder conversar sobre&lt;br /&gt;
+	Manual de cálculo EMP 2026  queremos saber cual es el documento del manual de calculo 2026 ya que no ha sido recibido aún&lt;br /&gt;
+	Estado de revisión de las propuestas técnicas enviadas en noviembre de 2025 en el marco del proceso 2026  en noviembre hicimos envío de nuestras apreciaciones y propuestas para el proceso de calculo de metas 2026 por lo que quisiéramos saber cuál fue el resultado de la revisión de ese documento por parte de la SIS.&lt;br /&gt;
+	Factibilidad y criterios asociados a la reliquidación en el grupo objetivo de mujeres embarazadas  vemos como riesgo no poder reliquidar el grupo embarazadas ya que es una condición que nos enteramos de manera posterior al igual como se indica en el manual  por lo que queremos saber si se podrá reliquidar este grupo.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Carolina Hidalgo Guajardo</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Isapre Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>javiera hartmann</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Isapre Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Carolina Marín Lopez</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Isapre Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/900137</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AO006AW2150075</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:00:00-04</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Metodología y cálculo del proceso de verificación de adecuación de precios base</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Francisco Antonio Rodriguez</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Isapre Consalud S.A.</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ignacio González</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>OCTAVIO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/900138</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>AO006AW2158805</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:00:00-04</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alameda 1449</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos., 
+Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Presentación de Modelo de Integral de Salud.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Andrés Guimpert Guridi</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Marcela Palma</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Carolina Hidalgo Guajardo</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Juan Guillermo Plaza</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/900135</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AO006AW2148803</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:30:00-04</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Videoconferencia.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Resultado de la verificación realizada para la adecuación de los precios base de los planes de salud</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Cristóbal Torres</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Isaias Ellez Millar</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ISALUD ISAPRE DE CODELCO SpA</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/900134</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>AO006AW2144697</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-04-09 16:00:00-04</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>videoconferencia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0 horas, 30 minutos</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Revisión de proceso de adecuación 2026 particularmente las diferencias en la verificación de la SIS y lo indicado por Esencial S.A con la finalidad de mejorar registros y proceso interno.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Maria Pia Andrioletti</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Carolina Hidalgo Guajardo</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/900132</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AO006AW2145588</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-04-09 15:00:00-04</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Videoconferencia</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>videoconferencia</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0 horas, 30 minutos</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>revisión cálculo de porcentaje de adecuación.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Hans Möller</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>COLMENA GOLDEN CROSS S.A.</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Colmena Golden Cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Mariela Barra</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Isapre Colmena</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Alejandro Cespedes</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Colmena</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881505</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AO006AW2088762</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos., 
+Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Mariela Barra</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Mariela Barra</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881499</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AO006AW2084767</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Alameda 1449. Ingreso por Piso 5</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos., 
+Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Maria Pia Andrioletti</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>ESENCIAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Carolina Hidalgo Guajardo</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ESENCIAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881498</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>AO006AW2085124</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2. Ingreso por piso 5</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Índice de Costos de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Francisco Antonio Rodriguez</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Isapre Consalud S.A.</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>OCTAVIO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>ISAPRE CONSALUD S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881506</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>AO006AW2089293</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Blas Duarte</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Bupa Chile S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Sebastián Navarrete</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Bupa Chile S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Alicia Alvarado</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Bupa Chile S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881500</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>AO006AW2088648</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Carlos Osorio</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Isapre Fundación BancoEstado</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Isapre Fundación BancoEstado</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881501</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>AO006AW2085341</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Macarena Bravo</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Optima S.A.</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Marcelo Vargas</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Daniela Verdugo</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Nueva Masvida</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881502</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AO006AW2085612</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Celebración, modificación o terminación a cualquier título, de contratos que realicen los sujetos pasivos y que sean necesarios para su funcionamiento.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Gonzalo Pulido</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>ISAPRE BANMEDICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PABLO BOCAS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>ISAPRE BANMEDICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881503</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>AO006AW2085709</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Diseño, implementación y evaluación de políticas, planes y programas efectuados por los sujetos pasivos., 
+Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Manuel Francisco Gana Mackenna</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Esencial S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>María Jeria</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Jefa del Departamento de Estudios y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://www.leylobby.gob.cl/instituciones/AO006/audiencias/2026/248901/881504</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AO006AW2085992</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:30:00-03</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Alameda 1449, torre 2 piso 5.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1 horas, 0 minutos</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Elaboración, dictación, modificación, denegación o rechazo de actos administrativos, proyectos de ley y leyes y también de las decisiones que tomen los sujetos pasivos.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Índice de Costo de Salud ICSA.</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Isaias Ellez Millar</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Gestor de intereses</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
         <is>
           <t>ISALUD ISAPRE DE CODELCO SpA</t>
         </is>
